--- a/Base_tratada.xlsx
+++ b/Base_tratada.xlsx
@@ -481,20 +481,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>Pedro Lucas Vieira</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C2" t="n">
+        <v>11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -513,10 +509,10 @@
         <v>3.8</v>
       </c>
       <c r="H2" t="n">
-        <v>63</v>
+        <v>63.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4.733333333333333</v>
+        <v>4.76</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -525,20 +521,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Emanuelly Moreira</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C3" t="n">
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -553,34 +545,32 @@
       <c r="F3" t="n">
         <v>8.4</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>7.8</v>
+      </c>
       <c r="H3" t="n">
-        <v>64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.933333333333334</v>
+        <v>7.55</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Murilo Nogueira</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C4" t="n">
+        <v>13</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -592,37 +582,35 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>8.1</v>
+      </c>
       <c r="G4" t="n">
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.433333333333334</v>
+        <v>7.15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Helena Oliveira</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C5" t="n">
+        <v>14</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -634,13 +622,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.4</v>
+      </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>2.166666666666667</v>
+        <v>4.55</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -649,20 +641,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Alice Ribeiro</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C6" t="n">
+        <v>15</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -674,15 +662,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>2.7</v>
+      </c>
       <c r="G6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>89</v>
+        <v>89.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5.866666666666667</v>
+        <v>6.79</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -691,20 +681,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Lucas Campos</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C7" t="n">
+        <v>12</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -716,13 +702,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.1</v>
+      </c>
       <c r="H7" t="n">
-        <v>76</v>
+        <v>76.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.533333333333333</v>
+        <v>6.89</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -731,20 +721,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Pedro Cavalcanti</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C8" t="n">
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -763,10 +749,10 @@
         <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.899999999999999</v>
+        <v>6.93</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -775,20 +761,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Bianca Pires</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C9" t="n">
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -803,12 +785,14 @@
       <c r="F9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="H9" t="n">
-        <v>61</v>
+        <v>61.9</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>5.23</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -817,20 +801,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Anthony da Mota</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C10" t="n">
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -849,10 +829,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>6.100000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -861,20 +841,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Nicole Gomes</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C11" t="n">
+        <v>13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -886,15 +862,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>5.7</v>
+      </c>
       <c r="G11" t="n">
         <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>83</v>
+        <v>83.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.966666666666667</v>
+        <v>5.88</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -903,20 +881,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Kevin Moraes</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C12" t="n">
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -928,15 +902,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>2.9</v>
+      </c>
       <c r="G12" t="n">
         <v>0.3</v>
       </c>
       <c r="H12" t="n">
-        <v>91</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3.133333333333333</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -945,20 +921,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Lavínia Costa</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C13" t="n">
+        <v>8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -973,12 +945,14 @@
       <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>8.1</v>
+      </c>
       <c r="H13" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -987,20 +961,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Lucca Nascimento</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C14" t="n">
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1015,12 +985,14 @@
       <c r="F14" t="n">
         <v>0.9</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>7.4</v>
+      </c>
       <c r="H14" t="n">
-        <v>81</v>
+        <v>81.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>5.49</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1029,20 +1001,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Luiz Gustavo Carvalho</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C15" t="n">
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1061,10 +1029,10 @@
         <v>6.5</v>
       </c>
       <c r="H15" t="n">
-        <v>62</v>
+        <v>62.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1073,20 +1041,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Miguel Teixeira</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C16" t="n">
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1101,34 +1065,32 @@
       <c r="F16" t="n">
         <v>7.7</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>8.6</v>
+      </c>
       <c r="H16" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>5.666666666666667</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Pietro Azevedo</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C17" t="n">
+        <v>11</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1143,12 +1105,14 @@
       <c r="F17" t="n">
         <v>0.8</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>6.8</v>
+      </c>
       <c r="H17" t="n">
         <v>84</v>
       </c>
       <c r="I17" t="n">
-        <v>3.066666666666667</v>
+        <v>5.33</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1157,20 +1121,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Larissa Araújo</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C18" t="n">
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1182,15 +1142,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>3.1</v>
+      </c>
       <c r="G18" t="n">
         <v>8</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>94.8</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>6.86</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1199,20 +1161,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Laura Correia</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C19" t="n">
+        <v>13</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1224,13 +1182,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.5</v>
+      </c>
       <c r="H19" t="n">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2.066666666666667</v>
+        <v>3.94</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1239,20 +1201,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Mariana Barbosa</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="C20" t="n">
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1271,10 +1229,10 @@
         <v>8.5</v>
       </c>
       <c r="H20" t="n">
-        <v>82</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>8.566666666666666</v>
+        <v>8.6</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1283,20 +1241,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Diego Moura</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C21" t="n">
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1315,10 +1269,10 @@
         <v>1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>5.366666666666667</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1327,20 +1281,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Guilherme Ramos</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C22" t="n">
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1352,15 +1302,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>2.8</v>
+      </c>
       <c r="G22" t="n">
         <v>0.9</v>
       </c>
       <c r="H22" t="n">
-        <v>91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>3.333333333333333</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1369,20 +1321,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Ana Nogueira</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C23" t="n">
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1394,35 +1342,35 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.8</v>
+      </c>
       <c r="H23" t="n">
-        <v>83</v>
+        <v>83.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.766666666666667</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Lorena Azevedo</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C24" t="n">
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1434,13 +1382,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.7</v>
+      </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>81.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>4.43</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1449,20 +1401,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Vitor Hugo Souza</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C25" t="n">
+        <v>12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1474,7 +1422,9 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>2.9</v>
+      </c>
       <c r="G25" t="n">
         <v>1.8</v>
       </c>
@@ -1482,7 +1432,7 @@
         <v>84</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1491,20 +1441,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Alícia Pereira</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C26" t="n">
+        <v>11</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1526,7 +1472,7 @@
         <v>68</v>
       </c>
       <c r="I26" t="n">
-        <v>4.733333333333333</v>
+        <v>4.73</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1535,20 +1481,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Noah Nogueira</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C27" t="n">
+        <v>9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1567,10 +1509,10 @@
         <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>80</v>
+        <v>80.5</v>
       </c>
       <c r="I27" t="n">
-        <v>4.533333333333333</v>
+        <v>4.55</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1579,20 +1521,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A28" t="n">
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Luigi Silva</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C28" t="n">
+        <v>12</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1607,12 +1545,14 @@
       <c r="F28" t="n">
         <v>0.8</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="H28" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="I28" t="n">
-        <v>3.433333333333334</v>
+        <v>6.21</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1621,20 +1561,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A29" t="n">
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>André Duarte</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C29" t="n">
+        <v>9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1649,12 +1585,14 @@
       <c r="F29" t="n">
         <v>2.2</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>2.9</v>
+      </c>
       <c r="H29" t="n">
         <v>69</v>
       </c>
       <c r="I29" t="n">
-        <v>3.033333333333334</v>
+        <v>4</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1663,20 +1601,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A30" t="n">
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Augusto Dias</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C30" t="n">
+        <v>6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1691,12 +1625,14 @@
       <c r="F30" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>3.3</v>
+      </c>
       <c r="H30" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="I30" t="n">
-        <v>4.933333333333333</v>
+        <v>6.06</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1705,20 +1641,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" t="n">
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Stella Correia</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C31" t="n">
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1737,10 +1669,10 @@
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="I31" t="n">
-        <v>5.766666666666667</v>
+        <v>5.77</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1749,20 +1681,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A32" t="n">
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Caroline Barbosa</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C32" t="n">
+        <v>14</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1774,15 +1702,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G32" t="n">
         <v>5.8</v>
       </c>
       <c r="H32" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="I32" t="n">
-        <v>4.466666666666666</v>
+        <v>5.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1791,20 +1721,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A33" t="n">
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Milena da Rosa</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C33" t="n">
+        <v>11</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1823,10 +1749,10 @@
         <v>1.2</v>
       </c>
       <c r="H33" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.766666666666667</v>
+        <v>4.78</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1835,20 +1761,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A34" t="n">
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Carolina da Mata</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C34" t="n">
+        <v>13</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1860,15 +1782,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G34" t="n">
         <v>0.9</v>
       </c>
       <c r="H34" t="n">
-        <v>75</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>4.56</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1877,20 +1801,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A35" t="n">
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Renan Novaes</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C35" t="n">
+        <v>10</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1902,13 +1822,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H35" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>5.44</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1917,20 +1841,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A36" t="n">
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Pedro Miguel Azevedo</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C36" t="n">
+        <v>9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1949,10 +1869,10 @@
         <v>0.1</v>
       </c>
       <c r="H36" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>5.433333333333333</v>
+        <v>5.45</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1961,20 +1881,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A37" t="n">
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Stella Peixoto</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C37" t="n">
+        <v>11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1993,10 +1909,10 @@
         <v>0.7</v>
       </c>
       <c r="H37" t="n">
-        <v>62</v>
+        <v>62.4</v>
       </c>
       <c r="I37" t="n">
-        <v>2.633333333333333</v>
+        <v>2.65</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2005,20 +1921,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A38" t="n">
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Rafael Pereira</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C38" t="n">
+        <v>14</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2030,13 +1942,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7.1</v>
+      </c>
       <c r="H38" t="n">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2.033333333333333</v>
+        <v>6.88</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2045,20 +1961,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A39" t="n">
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>João Pedro Rodrigues</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C39" t="n">
+        <v>11</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2077,10 +1989,10 @@
         <v>0.4</v>
       </c>
       <c r="H39" t="n">
-        <v>85</v>
+        <v>85.7</v>
       </c>
       <c r="I39" t="n">
-        <v>6.166666666666667</v>
+        <v>6.19</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2089,20 +2001,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A40" t="n">
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Yago Freitas</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C40" t="n">
+        <v>9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2121,10 +2029,10 @@
         <v>7.3</v>
       </c>
       <c r="H40" t="n">
-        <v>73</v>
+        <v>73.7</v>
       </c>
       <c r="I40" t="n">
-        <v>8.066666666666666</v>
+        <v>8.09</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2133,20 +2041,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A41" t="n">
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Nathan Farias</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C41" t="n">
+        <v>8</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2161,12 +2065,14 @@
       <c r="F41" t="n">
         <v>2.7</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="H41" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="I41" t="n">
-        <v>3.133333333333333</v>
+        <v>6.38</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2175,20 +2081,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A42" t="n">
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Fernando Pinto</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C42" t="n">
+        <v>8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2203,34 +2105,32 @@
       <c r="F42" t="n">
         <v>9.5</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>6.5</v>
+      </c>
       <c r="H42" t="n">
-        <v>93</v>
+        <v>93.3</v>
       </c>
       <c r="I42" t="n">
-        <v>6.266666666666667</v>
+        <v>8.44</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Sofia Gomes</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="C43" t="n">
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2242,35 +2142,35 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.2</v>
+      </c>
       <c r="H43" t="n">
-        <v>86</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>2.866666666666667</v>
+        <v>7.46</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A44" t="n">
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Emanuel Silveira</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C44" t="n">
+        <v>9</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2289,10 +2189,10 @@
         <v>3.9</v>
       </c>
       <c r="H44" t="n">
-        <v>62</v>
+        <v>62.9</v>
       </c>
       <c r="I44" t="n">
-        <v>3.366666666666667</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2301,20 +2201,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A45" t="n">
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Nina Moreira</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C45" t="n">
+        <v>10</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2326,13 +2222,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.3</v>
+      </c>
       <c r="H45" t="n">
         <v>66</v>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>5.27</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2341,20 +2241,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="A46" t="n">
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Emanuelly Viana</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C46" t="n">
+        <v>14</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2366,15 +2262,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G46" t="n">
         <v>6.9</v>
       </c>
       <c r="H46" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="I46" t="n">
-        <v>4.333333333333333</v>
+        <v>5.84</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2383,20 +2281,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A47" t="n">
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Helena Almeida</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C47" t="n">
+        <v>7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2408,15 +2302,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>7.6</v>
+      </c>
       <c r="G47" t="n">
         <v>4.8</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
+        <v>60.8</v>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>6.16</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2425,20 +2321,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="A48" t="n">
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Vitória Martins</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C48" t="n">
+        <v>10</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2453,12 +2345,14 @@
       <c r="F48" t="n">
         <v>5.5</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>2.5</v>
+      </c>
       <c r="H48" t="n">
         <v>65</v>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>4.83</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2467,20 +2361,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="A49" t="n">
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Henrique Santos</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C49" t="n">
+        <v>13</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2492,13 +2382,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.4</v>
+      </c>
       <c r="H49" t="n">
-        <v>77</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>2.566666666666667</v>
+        <v>5.75</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2507,20 +2401,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="A50" t="n">
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Caio Costela</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C50" t="n">
+        <v>13</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2532,13 +2422,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.9</v>
+      </c>
       <c r="H50" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>2.366666666666667</v>
+        <v>6.07</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2547,20 +2441,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="A51" t="n">
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Rodrigo Caldeira</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C51" t="n">
+        <v>7</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2572,13 +2462,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3.3</v>
+      </c>
       <c r="H51" t="n">
         <v>89</v>
       </c>
       <c r="I51" t="n">
-        <v>2.966666666666667</v>
+        <v>4.9</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2587,20 +2481,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="A52" t="n">
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Marcos Vinicius Lopes</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C52" t="n">
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2612,35 +2502,35 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.1</v>
+      </c>
       <c r="H52" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>7.61</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A53" t="n">
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Enzo Aragão</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C53" t="n">
+        <v>8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2659,10 +2549,10 @@
         <v>4.8</v>
       </c>
       <c r="H53" t="n">
-        <v>97</v>
+        <v>97.2</v>
       </c>
       <c r="I53" t="n">
-        <v>6.033333333333334</v>
+        <v>6.04</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2671,20 +2561,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="A54" t="n">
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Leandro Peixoto</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C54" t="n">
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2703,10 +2589,10 @@
         <v>5.9</v>
       </c>
       <c r="H54" t="n">
-        <v>94</v>
+        <v>94.8</v>
       </c>
       <c r="I54" t="n">
-        <v>6.733333333333334</v>
+        <v>6.76</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2715,20 +2601,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="A55" t="n">
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Isabelly Novaes</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C55" t="n">
+        <v>11</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2747,10 +2629,10 @@
         <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>7.333333333333333</v>
+        <v>7.35</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2759,20 +2641,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A56" t="n">
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Gustavo Ribeiro</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C56" t="n">
+        <v>12</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2791,10 +2669,10 @@
         <v>0.2</v>
       </c>
       <c r="H56" t="n">
-        <v>87</v>
+        <v>87.8</v>
       </c>
       <c r="I56" t="n">
-        <v>5.533333333333334</v>
+        <v>5.56</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2803,20 +2681,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="A57" t="n">
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>João Lopes</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C57" t="n">
+        <v>10</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2828,13 +2702,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5.1</v>
+      </c>
       <c r="H57" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>6.28</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2843,20 +2721,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A58" t="n">
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Maria Sophia Cardoso</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C58" t="n">
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2868,15 +2742,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>2.7</v>
+      </c>
       <c r="G58" t="n">
         <v>1.3</v>
       </c>
       <c r="H58" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>4.21</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2885,20 +2761,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A59" t="n">
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Natália Teixeira</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C59" t="n">
+        <v>13</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2913,12 +2785,14 @@
       <c r="F59" t="n">
         <v>3.2</v>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>3.1</v>
+      </c>
       <c r="H59" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="I59" t="n">
-        <v>3.533333333333334</v>
+        <v>4.58</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2927,20 +2801,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="A60" t="n">
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Lívia Alves</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C60" t="n">
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2952,13 +2822,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.2</v>
+      </c>
       <c r="H60" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2967,20 +2841,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A61" t="n">
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Alana da Rosa</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C61" t="n">
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2995,12 +2865,14 @@
       <c r="F61" t="n">
         <v>5.8</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>5.7</v>
+      </c>
       <c r="H61" t="n">
-        <v>74</v>
+        <v>74.2</v>
       </c>
       <c r="I61" t="n">
-        <v>4.399999999999999</v>
+        <v>6.31</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3009,20 +2881,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="A62" t="n">
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Alice Ferreira</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C62" t="n">
+        <v>9</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3037,12 +2905,14 @@
       <c r="F62" t="n">
         <v>6.1</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>3.7</v>
+      </c>
       <c r="H62" t="n">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>4.433333333333334</v>
+        <v>5.68</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3051,20 +2921,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="A63" t="n">
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Evelyn Pinto</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C63" t="n">
+        <v>7</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3083,10 +2949,10 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>3.200000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3095,20 +2961,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="A64" t="n">
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Renan Nogueira</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C64" t="n">
+        <v>13</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3127,10 +2989,10 @@
         <v>5.1</v>
       </c>
       <c r="H64" t="n">
-        <v>93</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>8.133333333333333</v>
+        <v>8.16</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3139,20 +3001,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A65" t="n">
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Maria Cecília Peixoto</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C65" t="n">
+        <v>12</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3164,37 +3022,35 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>5.3</v>
+      </c>
       <c r="G65" t="n">
         <v>8.9</v>
       </c>
       <c r="H65" t="n">
-        <v>80</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>5.633333333333333</v>
+        <v>7.42</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A66" t="n">
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Maysa Aragão</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C66" t="n">
+        <v>12</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3213,10 +3069,10 @@
         <v>0.5</v>
       </c>
       <c r="H66" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="I66" t="n">
-        <v>3.633333333333333</v>
+        <v>3.66</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3225,20 +3081,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="A67" t="n">
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Laís Farias</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C67" t="n">
+        <v>15</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3250,15 +3102,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>4.6</v>
+      </c>
       <c r="G67" t="n">
         <v>2.5</v>
       </c>
       <c r="H67" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="I67" t="n">
-        <v>4.100000000000001</v>
+        <v>5.65</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3267,20 +3121,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="A68" t="n">
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Manuela da Cruz</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C68" t="n">
+        <v>9</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3292,15 +3142,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>4.2</v>
+      </c>
       <c r="G68" t="n">
         <v>4</v>
       </c>
       <c r="H68" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="I68" t="n">
-        <v>3.333333333333333</v>
+        <v>4.74</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3309,20 +3161,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="A69" t="n">
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Daniela Costela</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C69" t="n">
+        <v>11</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3337,12 +3185,14 @@
       <c r="F69" t="n">
         <v>4.7</v>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>6.4</v>
+      </c>
       <c r="H69" t="n">
-        <v>79</v>
+        <v>79.7</v>
       </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>6.36</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3351,20 +3201,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="A70" t="n">
+        <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Kamilly Freitas</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C70" t="n">
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3383,10 +3229,10 @@
         <v>3.6</v>
       </c>
       <c r="H70" t="n">
-        <v>71</v>
+        <v>71.5</v>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3395,20 +3241,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="A71" t="n">
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Ana Vitória Almeida</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C71" t="n">
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3423,12 +3265,14 @@
       <c r="F71" t="n">
         <v>9</v>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>1.1</v>
+      </c>
       <c r="H71" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>5.833333333333333</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3437,20 +3281,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="A72" t="n">
+        <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Pietro Almeida</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C72" t="n">
+        <v>12</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3469,10 +3309,10 @@
         <v>9</v>
       </c>
       <c r="H72" t="n">
-        <v>91</v>
+        <v>91.2</v>
       </c>
       <c r="I72" t="n">
-        <v>8.133333333333333</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3481,20 +3321,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="A73" t="n">
+        <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Júlia Cardoso</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C73" t="n">
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3509,34 +3345,32 @@
       <c r="F73" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>6.2</v>
+      </c>
       <c r="H73" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>7.09</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A74" t="n">
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Marcela das Neves</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C74" t="n">
+        <v>13</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3555,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="H74" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>6.033333333333332</v>
+        <v>6.06</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3567,20 +3401,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="A75" t="n">
+        <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>João Miguel Moura</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C75" t="n">
+        <v>7</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3599,10 +3429,10 @@
         <v>9.1</v>
       </c>
       <c r="H75" t="n">
-        <v>85</v>
+        <v>85.3</v>
       </c>
       <c r="I75" t="n">
-        <v>6.633333333333333</v>
+        <v>6.64</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3611,20 +3441,16 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A76" t="n">
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Maria Luiza Silva</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C76" t="n">
+        <v>10</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3639,34 +3465,32 @@
       <c r="F76" t="n">
         <v>5.6</v>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>8.1</v>
+      </c>
       <c r="H76" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="I76" t="n">
-        <v>5.133333333333334</v>
+        <v>7.86</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A77" t="n">
+        <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Mirella Viana</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C77" t="n">
+        <v>11</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3678,37 +3502,35 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>6.2</v>
+      </c>
       <c r="G77" t="n">
         <v>9</v>
       </c>
       <c r="H77" t="n">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>5.899999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A78" t="n">
+        <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Ana Carolina Farias</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C78" t="n">
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3720,13 +3542,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8.6</v>
+      </c>
       <c r="H78" t="n">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>3.233333333333333</v>
+        <v>6.73</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3735,20 +3561,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A79" t="n">
+        <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Isabelly Nogueira</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C79" t="n">
+        <v>8</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3763,12 +3585,14 @@
       <c r="F79" t="n">
         <v>6</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>3.9</v>
+      </c>
       <c r="H79" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>4.433333333333334</v>
+        <v>5.75</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3777,20 +3601,16 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="A80" t="n">
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Emilly Pereira</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C80" t="n">
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3805,12 +3625,14 @@
       <c r="F80" t="n">
         <v>1.9</v>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>1.8</v>
+      </c>
       <c r="H80" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>3.51</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3819,20 +3641,16 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="A81" t="n">
+        <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Juliana Lima</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C81" t="n">
+        <v>14</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3851,10 +3669,10 @@
         <v>6.7</v>
       </c>
       <c r="H81" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="I81" t="n">
-        <v>5.133333333333333</v>
+        <v>5.15</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3863,20 +3681,16 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="A82" t="n">
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Maria Luiza Souza</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C82" t="n">
+        <v>9</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3895,10 +3709,10 @@
         <v>4.4</v>
       </c>
       <c r="H82" t="n">
-        <v>77</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>5.399999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3907,20 +3721,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A83" t="n">
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Mirella Viana</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C83" t="n">
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3939,10 +3749,10 @@
         <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>7.433333333333334</v>
+        <v>7.46</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3951,20 +3761,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A84" t="n">
+        <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Heloísa Mendes</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C84" t="n">
+        <v>14</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3983,10 +3789,10 @@
         <v>5.5</v>
       </c>
       <c r="H84" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="I84" t="n">
-        <v>4.766666666666667</v>
+        <v>4.77</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3995,20 +3801,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A85" t="n">
+        <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Levi Azevedo</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C85" t="n">
+        <v>7</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4020,15 +3822,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G85" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>5.033333333333334</v>
+        <v>6.55</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4037,20 +3841,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="A86" t="n">
+        <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Leonardo Nunes</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C86" t="n">
+        <v>15</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4065,12 +3865,14 @@
       <c r="F86" t="n">
         <v>1.3</v>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H86" t="n">
-        <v>94</v>
+        <v>94.2</v>
       </c>
       <c r="I86" t="n">
-        <v>3.566666666666667</v>
+        <v>5.44</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4079,20 +3881,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="A87" t="n">
+        <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Felipe Teixeira</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C87" t="n">
+        <v>12</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -4104,13 +3902,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.1</v>
+      </c>
       <c r="H87" t="n">
-        <v>61</v>
+        <v>61.4</v>
       </c>
       <c r="I87" t="n">
-        <v>2.033333333333333</v>
+        <v>3.58</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4119,20 +3921,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="A88" t="n">
+        <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Daniela Aragão</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C88" t="n">
+        <v>10</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4147,12 +3945,14 @@
       <c r="F88" t="n">
         <v>0.5</v>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="H88" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>2.966666666666667</v>
+        <v>5.74</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4161,20 +3961,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="A89" t="n">
+        <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Vinicius Fogaça</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C89" t="n">
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4189,12 +3985,14 @@
       <c r="F89" t="n">
         <v>3.9</v>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>2.9</v>
+      </c>
       <c r="H89" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>4.033333333333333</v>
+        <v>5.01</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4203,20 +4001,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="A90" t="n">
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Daniela Rezende</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C90" t="n">
+        <v>6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4228,7 +4022,9 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>5.6</v>
+      </c>
       <c r="G90" t="n">
         <v>3.1</v>
       </c>
@@ -4236,7 +4032,7 @@
         <v>90</v>
       </c>
       <c r="I90" t="n">
-        <v>4.033333333333333</v>
+        <v>5.9</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4245,20 +4041,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="A91" t="n">
+        <v>90</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Luiz Fernando da Luz</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C91" t="n">
+        <v>15</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4277,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4289,20 +4081,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A92" t="n">
+        <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Davi Luiz Vieira</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C92" t="n">
+        <v>13</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -4314,15 +4102,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>8.9</v>
+      </c>
       <c r="G92" t="n">
         <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>82</v>
+        <v>82.7</v>
       </c>
       <c r="I92" t="n">
-        <v>3.733333333333333</v>
+        <v>6.72</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4331,20 +4121,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="A93" t="n">
+        <v>92</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Samuel Campos</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="C93" t="n">
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4356,15 +4142,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>7.3</v>
+      </c>
       <c r="G93" t="n">
         <v>4.9</v>
       </c>
       <c r="H93" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="I93" t="n">
-        <v>4.033333333333334</v>
+        <v>6.48</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4373,20 +4161,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="A94" t="n">
+        <v>93</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Agatha Campos</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C94" t="n">
+        <v>12</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4398,15 +4182,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="G94" t="n">
         <v>0.3</v>
       </c>
       <c r="H94" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>3.066666666666667</v>
+        <v>5.8</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4415,20 +4201,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="A95" t="n">
+        <v>94</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Bernardo Peixoto</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C95" t="n">
+        <v>7</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -4443,12 +4225,14 @@
       <c r="F95" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="n">
+        <v>1.9</v>
+      </c>
       <c r="H95" t="n">
-        <v>75</v>
+        <v>75.8</v>
       </c>
       <c r="I95" t="n">
-        <v>5.733333333333333</v>
+        <v>6.39</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4457,20 +4241,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A96" t="n">
+        <v>95</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Pedro Lucas da Mata</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C96" t="n">
+        <v>14</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -4482,13 +4262,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.2</v>
+      </c>
       <c r="H96" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="I96" t="n">
-        <v>2.866666666666667</v>
+        <v>5.65</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4497,20 +4281,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A97" t="n">
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Julia das Neves</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="C97" t="n">
+        <v>15</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -4525,12 +4305,14 @@
       <c r="F97" t="n">
         <v>2.9</v>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>5.3</v>
+      </c>
       <c r="H97" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I97" t="n">
-        <v>3.566666666666666</v>
+        <v>5.34</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4539,20 +4321,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A98" t="n">
+        <v>97</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>João Ramos</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C98" t="n">
+        <v>6</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -4567,34 +4345,32 @@
       <c r="F98" t="n">
         <v>9.9</v>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>7.1</v>
+      </c>
       <c r="H98" t="n">
-        <v>71</v>
+        <v>71.8</v>
       </c>
       <c r="I98" t="n">
-        <v>5.666666666666667</v>
+        <v>8.06</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="A99" t="n">
+        <v>98</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Clarice da Mota</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C99" t="n">
+        <v>8</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -4613,32 +4389,28 @@
         <v>3.5</v>
       </c>
       <c r="H99" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="I99" t="n">
-        <v>5.533333333333334</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Lucas Gabriel da Luz</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C100" t="n">
+        <v>11</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -4650,15 +4422,17 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G100" t="n">
         <v>1.2</v>
       </c>
       <c r="H100" t="n">
-        <v>63</v>
+        <v>63.6</v>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>4.02</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4667,20 +4441,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A101" t="n">
+        <v>100</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Ana Sophia Nunes</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="C101" t="n">
+        <v>8</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -4692,15 +4462,17 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>2.2</v>
+      </c>
       <c r="G101" t="n">
         <v>5</v>
       </c>
       <c r="H101" t="n">
-        <v>60</v>
+        <v>60.7</v>
       </c>
       <c r="I101" t="n">
-        <v>3.666666666666667</v>
+        <v>4.42</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
